--- a/raw/한화.xlsx
+++ b/raw/한화.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/920678a7b799b336/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{77A55D82-CB42-4087-B12F-F2B94D90495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E151399-3905-4198-81B1-EDA9B4BA2B3F}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{77A55D82-CB42-4087-B12F-F2B94D90495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAC67966-F6F2-433F-8633-025CAA5A2F92}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AC7A5A0F-CEDA-47FF-A964-62C58C6A3FEA}"/>
   </bookViews>
@@ -40,9 +40,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="84">
-  <si>
-    <t>순위</t>
-  </si>
   <si>
     <t>선수명</t>
   </si>
@@ -292,6 +289,10 @@
   <si>
     <t>신지후</t>
   </si>
+  <si>
+    <t>년도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -397,7 +398,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -425,13 +426,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="12" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -450,6 +445,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,64 +773,64 @@
   <sheetData>
     <row r="1" spans="1:20" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="18" thickBot="1">
@@ -839,10 +838,10 @@
         <v>2026</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4">
         <v>6</v>
@@ -863,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K2" s="3">
         <v>20</v>
@@ -901,10 +900,10 @@
         <v>2026</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4">
         <v>6</v>
@@ -925,7 +924,7 @@
         <v>2</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3">
         <v>25</v>
@@ -963,10 +962,10 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4">
         <v>5</v>
@@ -987,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" s="3">
         <v>21</v>
@@ -1025,10 +1024,10 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4">
         <v>5</v>
@@ -1049,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" s="3">
         <v>19</v>
@@ -1087,10 +1086,10 @@
         <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4">
         <v>4</v>
@@ -1111,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" s="3">
         <v>24</v>
@@ -1149,10 +1148,10 @@
         <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
@@ -1211,10 +1210,10 @@
         <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4">
         <v>3</v>
@@ -1273,10 +1272,10 @@
         <v>2026</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4">
         <v>3</v>
@@ -1335,10 +1334,10 @@
         <v>2026</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4">
         <v>2</v>
@@ -1359,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="3">
         <v>27</v>
@@ -1397,10 +1396,10 @@
         <v>2026</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4">
         <v>2</v>
@@ -1459,31 +1458,31 @@
         <v>2026</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K12" s="3">
         <v>8</v>
@@ -1521,31 +1520,31 @@
         <v>2026</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K13" s="3">
         <v>15</v>
@@ -1583,10 +1582,10 @@
         <v>2026</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1607,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="3">
         <v>19</v>
@@ -1645,10 +1644,10 @@
         <v>2026</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1707,10 +1706,10 @@
         <v>2026</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1769,10 +1768,10 @@
         <v>2026</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1793,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K17" s="3">
         <v>20</v>
@@ -1831,31 +1830,31 @@
         <v>2026</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K18" s="3">
         <v>5</v>
@@ -1893,31 +1892,31 @@
         <v>2026</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K19" s="3">
         <v>5</v>
@@ -1955,31 +1954,31 @@
         <v>2026</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K20" s="3">
         <v>3</v>
@@ -2017,10 +2016,10 @@
         <v>2026</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
@@ -2041,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K21" s="3">
         <v>7</v>
@@ -2079,10 +2078,10 @@
         <v>2026</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -2141,31 +2140,31 @@
         <v>2026</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K23" s="3">
         <v>3</v>
@@ -2203,10 +2202,10 @@
         <v>2026</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="8">
         <v>1</v>
@@ -2265,10 +2264,10 @@
         <v>2025</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4">
         <v>10</v>
@@ -2289,7 +2288,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K25" s="3">
         <v>32</v>
@@ -2327,10 +2326,10 @@
         <v>2025</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="4">
         <v>10</v>
@@ -2351,7 +2350,7 @@
         <v>2</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K26" s="3">
         <v>38</v>
@@ -2389,10 +2388,10 @@
         <v>2025</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4">
         <v>8</v>
@@ -2413,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K27" s="3">
         <v>27</v>
@@ -2451,10 +2450,10 @@
         <v>2025</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" s="4">
         <v>8</v>
@@ -2475,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K28" s="3">
         <v>38</v>
@@ -2513,10 +2512,10 @@
         <v>2025</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" s="4">
         <v>7</v>
@@ -2575,10 +2574,10 @@
         <v>2025</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="4">
         <v>7</v>
@@ -2599,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K30" s="3">
         <v>27</v>
@@ -2637,10 +2636,10 @@
         <v>2025</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="4">
         <v>6</v>
@@ -2661,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K31" s="3">
         <v>36</v>
@@ -2699,10 +2698,10 @@
         <v>2025</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4">
         <v>5</v>
@@ -2761,10 +2760,10 @@
         <v>2025</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4">
         <v>3</v>
@@ -2823,10 +2822,10 @@
         <v>2025</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D34" s="4">
         <v>3</v>
@@ -2885,10 +2884,10 @@
         <v>2025</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4">
         <v>3</v>
@@ -2947,10 +2946,10 @@
         <v>2025</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D36" s="4">
         <v>2</v>
@@ -2971,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K36" s="3">
         <v>13</v>
@@ -3009,10 +3008,10 @@
         <v>2025</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="4">
         <v>2</v>
@@ -3071,10 +3070,10 @@
         <v>2025</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
@@ -3133,31 +3132,31 @@
         <v>2025</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D39" s="4">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3">
-        <v>3</v>
-      </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K39" s="3">
         <v>15</v>
@@ -3195,31 +3194,31 @@
         <v>2025</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D40" s="4">
-        <v>2</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K40" s="3">
         <v>5</v>
@@ -3257,31 +3256,31 @@
         <v>2025</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="4">
+        <v>2</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D41" s="4">
-        <v>2</v>
-      </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K41" s="3">
         <v>5</v>
@@ -3319,17 +3318,17 @@
         <v>2025</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -3343,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K42" s="3">
         <v>4</v>
@@ -3380,61 +3379,61 @@
       <c r="A43" s="3">
         <v>2025</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="10">
-        <v>1</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9">
-        <v>0</v>
-      </c>
-      <c r="I43" s="9">
-        <v>0</v>
-      </c>
-      <c r="J43" s="9">
-        <v>1</v>
-      </c>
-      <c r="K43" s="9">
+      <c r="B43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="8">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <v>1</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7">
+        <v>1</v>
+      </c>
+      <c r="K43" s="7">
         <v>23</v>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="7">
         <v>6</v>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="7">
         <v>6</v>
       </c>
-      <c r="N43" s="9">
-        <v>0</v>
-      </c>
-      <c r="O43" s="9">
-        <v>1</v>
-      </c>
-      <c r="P43" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="9">
+      <c r="N43" s="7">
+        <v>0</v>
+      </c>
+      <c r="O43" s="7">
+        <v>1</v>
+      </c>
+      <c r="P43" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
         <v>8</v>
       </c>
-      <c r="R43" s="9">
-        <v>0</v>
-      </c>
-      <c r="S43" s="9">
-        <v>0</v>
-      </c>
-      <c r="T43" s="9">
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <v>0</v>
+      </c>
+      <c r="T43" s="7">
         <v>0.27300000000000002</v>
       </c>
     </row>
@@ -3443,10 +3442,10 @@
         <v>2024</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" s="4">
         <v>9</v>
@@ -3505,10 +3504,10 @@
         <v>2024</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" s="4">
         <v>7</v>
@@ -3529,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K45" s="3">
         <v>34</v>
@@ -3567,10 +3566,10 @@
         <v>2024</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46" s="4">
         <v>7</v>
@@ -3629,10 +3628,10 @@
         <v>2024</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47" s="4">
         <v>6</v>
@@ -3653,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K47" s="3">
         <v>25</v>
@@ -3691,10 +3690,10 @@
         <v>2024</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D48" s="4">
         <v>6</v>
@@ -3715,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K48" s="3">
         <v>27</v>
@@ -3753,10 +3752,10 @@
         <v>2024</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D49" s="4">
         <v>6</v>
@@ -3815,10 +3814,10 @@
         <v>2024</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50" s="4">
         <v>5</v>
@@ -3877,10 +3876,10 @@
         <v>2024</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D51" s="4">
         <v>4</v>
@@ -3901,7 +3900,7 @@
         <v>2</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K51" s="3">
         <v>17</v>
@@ -3939,10 +3938,10 @@
         <v>2024</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" s="4">
         <v>4</v>
@@ -3963,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K52" s="3">
         <v>19</v>
@@ -4001,10 +4000,10 @@
         <v>2024</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" s="4">
         <v>4</v>
@@ -4063,10 +4062,10 @@
         <v>2024</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D54" s="4">
         <v>3</v>
@@ -4125,10 +4124,10 @@
         <v>2024</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D55" s="4">
         <v>3</v>
@@ -4187,10 +4186,10 @@
         <v>2024</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D56" s="4">
         <v>3</v>
@@ -4211,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K56" s="3">
         <v>16</v>
@@ -4249,10 +4248,10 @@
         <v>2024</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D57" s="4">
         <v>3</v>
@@ -4311,10 +4310,10 @@
         <v>2024</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D58" s="4">
         <v>2</v>
@@ -4373,10 +4372,10 @@
         <v>2024</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" s="4">
         <v>2</v>
@@ -4397,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K59" s="3">
         <v>12</v>
@@ -4435,10 +4434,10 @@
         <v>2024</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D60" s="4">
         <v>1</v>
@@ -4497,10 +4496,10 @@
         <v>2024</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D61" s="4">
         <v>1</v>
@@ -4521,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K61" s="3">
         <v>23</v>
@@ -4559,31 +4558,31 @@
         <v>2024</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D62" s="4">
-        <v>1</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K62" s="3">
         <v>5</v>
@@ -4621,10 +4620,10 @@
         <v>2024</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D63" s="4">
         <v>1</v>
@@ -4682,61 +4681,61 @@
       <c r="A64" s="3">
         <v>2024</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" s="9" t="s">
+      <c r="B64" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="8">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7">
+        <v>0</v>
+      </c>
+      <c r="H64" s="7">
+        <v>0</v>
+      </c>
+      <c r="I64" s="7">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="10">
-        <v>1</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0</v>
-      </c>
-      <c r="F64" s="9">
-        <v>0</v>
-      </c>
-      <c r="G64" s="9">
-        <v>0</v>
-      </c>
-      <c r="H64" s="9">
-        <v>0</v>
-      </c>
-      <c r="I64" s="9">
-        <v>0</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K64" s="9">
+      <c r="K64" s="7">
         <v>4</v>
       </c>
-      <c r="L64" s="11">
+      <c r="L64" s="9">
         <v>1.3333333333333333</v>
       </c>
-      <c r="M64" s="9">
-        <v>1</v>
-      </c>
-      <c r="N64" s="9">
-        <v>0</v>
-      </c>
-      <c r="O64" s="9">
-        <v>0</v>
-      </c>
-      <c r="P64" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="9">
-        <v>0</v>
-      </c>
-      <c r="R64" s="9">
-        <v>0</v>
-      </c>
-      <c r="S64" s="9">
-        <v>0</v>
-      </c>
-      <c r="T64" s="9">
+      <c r="M64" s="7">
+        <v>1</v>
+      </c>
+      <c r="N64" s="7">
+        <v>0</v>
+      </c>
+      <c r="O64" s="7">
+        <v>0</v>
+      </c>
+      <c r="P64" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="7">
+        <v>0</v>
+      </c>
+      <c r="R64" s="7">
+        <v>0</v>
+      </c>
+      <c r="S64" s="7">
+        <v>0</v>
+      </c>
+      <c r="T64" s="7">
         <v>0.25</v>
       </c>
     </row>
@@ -4745,10 +4744,10 @@
         <v>2023</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" s="4">
         <v>9</v>
@@ -4807,10 +4806,10 @@
         <v>2023</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D66" s="4">
         <v>8</v>
@@ -4869,10 +4868,10 @@
         <v>2023</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D67" s="4">
         <v>5</v>
@@ -4893,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K67" s="3">
         <v>22</v>
@@ -4931,10 +4930,10 @@
         <v>2023</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D68" s="4">
         <v>5</v>
@@ -4955,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K68" s="3">
         <v>45</v>
@@ -4993,10 +4992,10 @@
         <v>2023</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D69" s="4">
         <v>5</v>
@@ -5017,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K69" s="3">
         <v>17</v>
@@ -5055,10 +5054,10 @@
         <v>2023</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D70" s="4">
         <v>5</v>
@@ -5117,10 +5116,10 @@
         <v>2023</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D71" s="4">
         <v>5</v>
@@ -5179,10 +5178,10 @@
         <v>2023</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D72" s="4">
         <v>4</v>
@@ -5241,10 +5240,10 @@
         <v>2023</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D73" s="4">
         <v>4</v>
@@ -5303,10 +5302,10 @@
         <v>2023</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D74" s="4">
         <v>4</v>
@@ -5327,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K74" s="3">
         <v>15</v>
@@ -5365,10 +5364,10 @@
         <v>2023</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D75" s="4">
         <v>4</v>
@@ -5427,31 +5426,31 @@
         <v>2023</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" s="4">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D76" s="4">
-        <v>3</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K76" s="3">
         <v>14</v>
@@ -5489,10 +5488,10 @@
         <v>2023</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D77" s="4">
         <v>3</v>
@@ -5551,31 +5550,31 @@
         <v>2023</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="4">
+        <v>2</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D78" s="4">
-        <v>2</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3">
-        <v>0</v>
-      </c>
-      <c r="H78" s="3">
-        <v>0</v>
-      </c>
-      <c r="I78" s="3">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K78" s="3">
         <v>7</v>
@@ -5613,10 +5612,10 @@
         <v>2023</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D79" s="4">
         <v>2</v>
@@ -5675,10 +5674,10 @@
         <v>2023</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D80" s="4">
         <v>2</v>
@@ -5737,10 +5736,10 @@
         <v>2023</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D81" s="4">
         <v>2</v>
@@ -5799,31 +5798,31 @@
         <v>2023</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="4">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D82" s="4">
-        <v>2</v>
-      </c>
-      <c r="E82" s="3">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3">
-        <v>0</v>
-      </c>
-      <c r="H82" s="3">
-        <v>0</v>
-      </c>
-      <c r="I82" s="3">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K82" s="3">
         <v>5</v>
@@ -5861,10 +5860,10 @@
         <v>2023</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D83" s="4">
         <v>1</v>
@@ -5885,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K83" s="3">
         <v>6</v>
@@ -5923,10 +5922,10 @@
         <v>2023</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D84" s="4">
         <v>1</v>
@@ -5947,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K84" s="3">
         <v>4</v>
@@ -5984,61 +5983,61 @@
       <c r="A85" s="3">
         <v>2023</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C85" s="9" t="s">
+      <c r="B85" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D85" s="8">
+        <v>1</v>
+      </c>
+      <c r="E85" s="7">
+        <v>6.75</v>
+      </c>
+      <c r="F85" s="7">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7">
+        <v>0</v>
+      </c>
+      <c r="H85" s="7">
+        <v>0</v>
+      </c>
+      <c r="I85" s="7">
+        <v>0</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="10">
-        <v>1</v>
-      </c>
-      <c r="E85" s="9">
-        <v>6.75</v>
-      </c>
-      <c r="F85" s="9">
-        <v>0</v>
-      </c>
-      <c r="G85" s="9">
-        <v>0</v>
-      </c>
-      <c r="H85" s="9">
-        <v>0</v>
-      </c>
-      <c r="I85" s="9">
-        <v>0</v>
-      </c>
-      <c r="J85" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K85" s="9">
+      <c r="K85" s="7">
         <v>5</v>
       </c>
-      <c r="L85" s="11">
+      <c r="L85" s="9">
         <v>1.3333333333333333</v>
       </c>
-      <c r="M85" s="9">
-        <v>1</v>
-      </c>
-      <c r="N85" s="9">
-        <v>1</v>
-      </c>
-      <c r="O85" s="9">
-        <v>0</v>
-      </c>
-      <c r="P85" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>0</v>
-      </c>
-      <c r="R85" s="9">
-        <v>1</v>
-      </c>
-      <c r="S85" s="9">
-        <v>1</v>
-      </c>
-      <c r="T85" s="9">
+      <c r="M85" s="7">
+        <v>1</v>
+      </c>
+      <c r="N85" s="7">
+        <v>1</v>
+      </c>
+      <c r="O85" s="7">
+        <v>0</v>
+      </c>
+      <c r="P85" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="7">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7">
+        <v>1</v>
+      </c>
+      <c r="S85" s="7">
+        <v>1</v>
+      </c>
+      <c r="T85" s="7">
         <v>0.2</v>
       </c>
     </row>
@@ -6047,10 +6046,10 @@
         <v>2022</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D86" s="4">
         <v>11</v>
@@ -6109,10 +6108,10 @@
         <v>2022</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D87" s="4">
         <v>10</v>
@@ -6171,10 +6170,10 @@
         <v>2022</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D88" s="4">
         <v>8</v>
@@ -6195,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K88" s="3">
         <v>28</v>
@@ -6233,10 +6232,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D89" s="4">
         <v>7</v>
@@ -6295,10 +6294,10 @@
         <v>2022</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D90" s="4">
         <v>7</v>
@@ -6357,10 +6356,10 @@
         <v>2022</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D91" s="4">
         <v>7</v>
@@ -6381,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K91" s="3">
         <v>34</v>
@@ -6419,10 +6418,10 @@
         <v>2022</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D92" s="4">
         <v>5</v>
@@ -6443,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K92" s="3">
         <v>21</v>
@@ -6481,10 +6480,10 @@
         <v>2022</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D93" s="4">
         <v>5</v>
@@ -6505,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K93" s="3">
         <v>19</v>
@@ -6543,10 +6542,10 @@
         <v>2022</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D94" s="4">
         <v>4</v>
@@ -6605,10 +6604,10 @@
         <v>2022</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D95" s="4">
         <v>4</v>
@@ -6667,10 +6666,10 @@
         <v>2022</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D96" s="4">
         <v>4</v>
@@ -6729,31 +6728,31 @@
         <v>2022</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="4">
+        <v>3</v>
+      </c>
+      <c r="E97" s="3">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D97" s="4">
-        <v>3</v>
-      </c>
-      <c r="E97" s="3">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3">
-        <v>0</v>
-      </c>
-      <c r="I97" s="3">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K97" s="3">
         <v>11</v>
@@ -6791,10 +6790,10 @@
         <v>2022</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D98" s="4">
         <v>3</v>
@@ -6853,10 +6852,10 @@
         <v>2022</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D99" s="4">
         <v>2</v>
@@ -6915,10 +6914,10 @@
         <v>2022</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D100" s="4">
         <v>2</v>
@@ -6939,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K100" s="3">
         <v>9</v>
@@ -6977,31 +6976,31 @@
         <v>2022</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D101" s="4">
-        <v>1</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K101" s="3">
         <v>5</v>
@@ -7039,31 +7038,31 @@
         <v>2022</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="4">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D102" s="4">
-        <v>1</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K102" s="3">
         <v>3</v>
@@ -7101,31 +7100,31 @@
         <v>2022</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" s="4">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D103" s="4">
-        <v>1</v>
-      </c>
-      <c r="E103" s="3">
-        <v>0</v>
-      </c>
-      <c r="F103" s="3">
-        <v>0</v>
-      </c>
-      <c r="G103" s="3">
-        <v>0</v>
-      </c>
-      <c r="H103" s="3">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3">
-        <v>1</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K103" s="3">
         <v>3</v>
@@ -7163,31 +7162,31 @@
         <v>2022</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104" s="4">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D104" s="4">
-        <v>1</v>
-      </c>
-      <c r="E104" s="3">
-        <v>0</v>
-      </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3">
-        <v>0</v>
-      </c>
-      <c r="H104" s="3">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K104" s="3">
         <v>17</v>
@@ -7225,10 +7224,10 @@
         <v>2022</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D105" s="4">
         <v>1</v>
@@ -7249,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K105" s="3">
         <v>6</v>
@@ -7287,31 +7286,31 @@
         <v>2022</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D106" s="4">
-        <v>1</v>
-      </c>
-      <c r="E106" s="3">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3">
-        <v>0</v>
-      </c>
-      <c r="H106" s="3">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K106" s="3">
         <v>5</v>
@@ -7348,61 +7347,61 @@
       <c r="A107" s="3">
         <v>2022</v>
       </c>
-      <c r="B107" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D107" s="10">
-        <v>1</v>
-      </c>
-      <c r="E107" s="9">
+      <c r="B107" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" s="8">
+        <v>1</v>
+      </c>
+      <c r="E107" s="7">
         <v>3.6</v>
       </c>
-      <c r="F107" s="9">
-        <v>0</v>
-      </c>
-      <c r="G107" s="9">
-        <v>1</v>
-      </c>
-      <c r="H107" s="9">
-        <v>0</v>
-      </c>
-      <c r="I107" s="9">
-        <v>0</v>
-      </c>
-      <c r="J107" s="9">
-        <v>0</v>
-      </c>
-      <c r="K107" s="9">
-        <v>20</v>
-      </c>
-      <c r="L107" s="9">
+      <c r="F107" s="7">
+        <v>0</v>
+      </c>
+      <c r="G107" s="7">
+        <v>1</v>
+      </c>
+      <c r="H107" s="7">
+        <v>0</v>
+      </c>
+      <c r="I107" s="7">
+        <v>0</v>
+      </c>
+      <c r="J107" s="7">
+        <v>0</v>
+      </c>
+      <c r="K107" s="7">
+        <v>20</v>
+      </c>
+      <c r="L107" s="7">
         <v>5</v>
       </c>
-      <c r="M107" s="9">
+      <c r="M107" s="7">
         <v>5</v>
       </c>
-      <c r="N107" s="9">
-        <v>1</v>
-      </c>
-      <c r="O107" s="9">
-        <v>1</v>
-      </c>
-      <c r="P107" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="9">
+      <c r="N107" s="7">
+        <v>1</v>
+      </c>
+      <c r="O107" s="7">
+        <v>1</v>
+      </c>
+      <c r="P107" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="7">
         <v>4</v>
       </c>
-      <c r="R107" s="9">
-        <v>2</v>
-      </c>
-      <c r="S107" s="9">
-        <v>2</v>
-      </c>
-      <c r="T107" s="9">
+      <c r="R107" s="7">
+        <v>2</v>
+      </c>
+      <c r="S107" s="7">
+        <v>2</v>
+      </c>
+      <c r="T107" s="7">
         <v>0.26300000000000001</v>
       </c>
     </row>
@@ -7411,10 +7410,10 @@
         <v>2021</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D108" s="4">
         <v>8</v>
@@ -7473,10 +7472,10 @@
         <v>2021</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D109" s="4">
         <v>7</v>
@@ -7497,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K109" s="3">
         <v>35</v>
@@ -7535,10 +7534,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D110" s="4">
         <v>6</v>
@@ -7597,10 +7596,10 @@
         <v>2021</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D111" s="4">
         <v>6</v>
@@ -7659,10 +7658,10 @@
         <v>2021</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D112" s="4">
         <v>5</v>
@@ -7683,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K112" s="3">
         <v>14</v>
@@ -7721,10 +7720,10 @@
         <v>2021</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D113" s="4">
         <v>4</v>
@@ -7745,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K113" s="3">
         <v>14</v>
@@ -7783,10 +7782,10 @@
         <v>2021</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D114" s="4">
         <v>4</v>
@@ -7807,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K114" s="3">
         <v>17</v>
@@ -7845,10 +7844,10 @@
         <v>2021</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D115" s="4">
         <v>4</v>
@@ -7907,10 +7906,10 @@
         <v>2021</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D116" s="4">
         <v>4</v>
@@ -7969,10 +7968,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D117" s="4">
         <v>4</v>
@@ -7993,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K117" s="3">
         <v>13</v>
@@ -8031,10 +8030,10 @@
         <v>2021</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D118" s="4">
         <v>3</v>
@@ -8093,10 +8092,10 @@
         <v>2021</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D119" s="4">
         <v>3</v>
@@ -8155,10 +8154,10 @@
         <v>2021</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D120" s="4">
         <v>3</v>
@@ -8179,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K120" s="3">
         <v>16</v>
@@ -8217,10 +8216,10 @@
         <v>2021</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D121" s="4">
         <v>3</v>
@@ -8241,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K121" s="3">
         <v>18</v>
@@ -8279,31 +8278,31 @@
         <v>2021</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D122" s="4">
+        <v>2</v>
+      </c>
+      <c r="E122" s="3">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D122" s="4">
-        <v>2</v>
-      </c>
-      <c r="E122" s="3">
-        <v>0</v>
-      </c>
-      <c r="F122" s="3">
-        <v>0</v>
-      </c>
-      <c r="G122" s="3">
-        <v>0</v>
-      </c>
-      <c r="H122" s="3">
-        <v>0</v>
-      </c>
-      <c r="I122" s="3">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K122" s="3">
         <v>26</v>
@@ -8341,31 +8340,31 @@
         <v>2021</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" s="4">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D123" s="4">
-        <v>2</v>
-      </c>
-      <c r="E123" s="3">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3">
-        <v>0</v>
-      </c>
-      <c r="G123" s="3">
-        <v>0</v>
-      </c>
-      <c r="H123" s="3">
-        <v>0</v>
-      </c>
-      <c r="I123" s="3">
-        <v>0</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K123" s="3">
         <v>9</v>
@@ -8403,10 +8402,10 @@
         <v>2021</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D124" s="4">
         <v>2</v>
@@ -8427,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K124" s="3">
         <v>19</v>
@@ -8465,10 +8464,10 @@
         <v>2021</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D125" s="4">
         <v>2</v>
@@ -8489,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K125" s="3">
         <v>12</v>
@@ -8527,10 +8526,10 @@
         <v>2021</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D126" s="4">
         <v>2</v>
@@ -8551,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K126" s="3">
         <v>7</v>
@@ -8589,10 +8588,10 @@
         <v>2021</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D127" s="4">
         <v>2</v>
@@ -8613,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K127" s="3">
         <v>10</v>
@@ -8651,31 +8650,31 @@
         <v>2021</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" s="4">
+        <v>2</v>
+      </c>
+      <c r="E128" s="3">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D128" s="4">
-        <v>2</v>
-      </c>
-      <c r="E128" s="3">
-        <v>0</v>
-      </c>
-      <c r="F128" s="3">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3">
-        <v>0</v>
-      </c>
-      <c r="H128" s="3">
-        <v>0</v>
-      </c>
-      <c r="I128" s="3">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K128" s="3">
         <v>29</v>
@@ -8713,10 +8712,10 @@
         <v>2021</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D129" s="4">
         <v>1</v>
@@ -8775,31 +8774,31 @@
         <v>2021</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D130" s="4">
+        <v>1</v>
+      </c>
+      <c r="E130" s="3">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D130" s="4">
-        <v>1</v>
-      </c>
-      <c r="E130" s="3">
-        <v>0</v>
-      </c>
-      <c r="F130" s="3">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3">
-        <v>0</v>
-      </c>
-      <c r="H130" s="3">
-        <v>0</v>
-      </c>
-      <c r="I130" s="3">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K130" s="3">
         <v>1</v>
@@ -8837,31 +8836,31 @@
         <v>2021</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" s="4">
+        <v>1</v>
+      </c>
+      <c r="E131" s="3">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D131" s="4">
-        <v>1</v>
-      </c>
-      <c r="E131" s="3">
-        <v>0</v>
-      </c>
-      <c r="F131" s="3">
-        <v>0</v>
-      </c>
-      <c r="G131" s="3">
-        <v>0</v>
-      </c>
-      <c r="H131" s="3">
-        <v>0</v>
-      </c>
-      <c r="I131" s="3">
-        <v>0</v>
-      </c>
-      <c r="J131" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="K131" s="3">
         <v>2</v>
@@ -8899,10 +8898,10 @@
         <v>2021</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D132" s="4">
         <v>1</v>
@@ -8923,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K132" s="3">
         <v>15</v>
@@ -8960,61 +8959,61 @@
       <c r="A133" s="3">
         <v>2021</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C133" s="9" t="s">
+      <c r="B133" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" s="8">
+        <v>1</v>
+      </c>
+      <c r="E133" s="7">
+        <v>9</v>
+      </c>
+      <c r="F133" s="7">
+        <v>0</v>
+      </c>
+      <c r="G133" s="7">
+        <v>0</v>
+      </c>
+      <c r="H133" s="7">
+        <v>0</v>
+      </c>
+      <c r="I133" s="7">
+        <v>1</v>
+      </c>
+      <c r="J133" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D133" s="10">
-        <v>1</v>
-      </c>
-      <c r="E133" s="9">
-        <v>9</v>
-      </c>
-      <c r="F133" s="9">
-        <v>0</v>
-      </c>
-      <c r="G133" s="9">
-        <v>0</v>
-      </c>
-      <c r="H133" s="9">
-        <v>0</v>
-      </c>
-      <c r="I133" s="9">
-        <v>1</v>
-      </c>
-      <c r="J133" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K133" s="9">
+      <c r="K133" s="7">
         <v>4</v>
       </c>
-      <c r="L133" s="9">
-        <v>1</v>
-      </c>
-      <c r="M133" s="9">
-        <v>1</v>
-      </c>
-      <c r="N133" s="9">
-        <v>0</v>
-      </c>
-      <c r="O133" s="9">
-        <v>0</v>
-      </c>
-      <c r="P133" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="9">
-        <v>1</v>
-      </c>
-      <c r="R133" s="9">
-        <v>1</v>
-      </c>
-      <c r="S133" s="9">
-        <v>1</v>
-      </c>
-      <c r="T133" s="9">
+      <c r="L133" s="7">
+        <v>1</v>
+      </c>
+      <c r="M133" s="7">
+        <v>1</v>
+      </c>
+      <c r="N133" s="7">
+        <v>0</v>
+      </c>
+      <c r="O133" s="7">
+        <v>0</v>
+      </c>
+      <c r="P133" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="7">
+        <v>1</v>
+      </c>
+      <c r="R133" s="7">
+        <v>1</v>
+      </c>
+      <c r="S133" s="7">
+        <v>1</v>
+      </c>
+      <c r="T133" s="7">
         <v>0.33300000000000002</v>
       </c>
     </row>
